--- a/diseases/d059/2005-2009.xlsx
+++ b/diseases/d059/2005-2009.xlsx
@@ -1169,6 +1169,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1553,6 +1558,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2094,6 +2104,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2239,6 +2254,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2387,6 +2407,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2532,6 +2557,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2680,6 +2710,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2825,6 +2860,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2973,6 +3013,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3118,6 +3163,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3266,6 +3316,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3411,6 +3466,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3559,6 +3619,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3704,6 +3769,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3852,6 +3922,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3997,6 +4072,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4145,6 +4225,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4290,6 +4375,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4438,6 +4528,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4583,6 +4678,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4731,6 +4831,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4876,6 +4981,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5024,6 +5134,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5169,6 +5284,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10033,6 +10153,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11999,6 +12124,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16470,6 +16600,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16615,6 +16750,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16763,6 +16903,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16908,6 +17053,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17056,6 +17206,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17201,6 +17356,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17349,6 +17509,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17494,6 +17659,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17642,6 +17812,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17787,6 +17962,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17935,6 +18115,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18080,6 +18265,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18228,6 +18418,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18373,6 +18568,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18521,6 +18721,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18666,6 +18871,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18814,6 +19024,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18959,6 +19174,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19107,6 +19327,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19252,6 +19477,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19400,6 +19630,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19545,6 +19780,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25195,6 +25435,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27161,6 +27406,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32025,6 +32275,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32170,6 +32425,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO174" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32318,6 +32578,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO175" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32463,6 +32728,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO176" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32611,6 +32881,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO177" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32756,6 +33031,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO178" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32904,6 +33184,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO179" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33049,6 +33334,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33197,6 +33487,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO181" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33342,6 +33637,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO182" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33490,6 +33790,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO183" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33635,6 +33940,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO184" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33783,6 +34093,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO185" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33928,6 +34243,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO186" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34076,6 +34396,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO187" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34221,6 +34546,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO188" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34369,6 +34699,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO189" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34514,6 +34849,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO190" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34662,6 +35002,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO191" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34807,6 +35152,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34955,6 +35305,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO193" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35100,6 +35455,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO194" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40750,6 +41110,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO223" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42716,6 +43081,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO233" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47580,6 +47950,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO258" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47725,6 +48100,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO259" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47873,6 +48253,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO260" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48018,6 +48403,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO261" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48166,6 +48556,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO262" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48311,6 +48706,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO263" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48459,6 +48859,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO264" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48604,6 +49009,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO265" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48752,6 +49162,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO266" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48897,6 +49312,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA267" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO267" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49045,6 +49465,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA268" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO268" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49190,6 +49615,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO269" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49338,6 +49768,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO270" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49483,6 +49918,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO271" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49631,6 +50071,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA272" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO272" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49776,6 +50221,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO273" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49924,6 +50374,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO274" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50069,6 +50524,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO275" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50217,6 +50677,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA276" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO276" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50362,6 +50827,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO277" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50510,6 +50980,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA278" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO278" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50655,6 +51130,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA279" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO279" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56305,6 +56785,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA308" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO308" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58271,6 +58756,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA318" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO318" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63135,6 +63625,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA343" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO343" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63280,6 +63775,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA344" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO344" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63428,6 +63928,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA345" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO345" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63573,6 +64078,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA346" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO346" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63721,6 +64231,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA347" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO347" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63866,6 +64381,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA348" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO348" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64014,6 +64534,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA349" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO349" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64159,6 +64684,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA350" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO350" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64307,6 +64837,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA351" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO351" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64452,6 +64987,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA352" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO352" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64600,6 +65140,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA353" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO353" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64745,6 +65290,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA354" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO354" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64893,6 +65443,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA355" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO355" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65038,6 +65593,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA356" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO356" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65186,6 +65746,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA357" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO357" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65331,6 +65896,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA358" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO358" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65479,6 +66049,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA359" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO359" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65624,6 +66199,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA360" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO360" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65772,6 +66352,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA361" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO361" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65917,6 +66502,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA362" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO362" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66065,6 +66655,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA363" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO363" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66208,6 +66803,11 @@
       <c r="S364" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA364" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO364" t="inlineStr">

--- a/diseases/d059/2005-2009.xlsx
+++ b/diseases/d059/2005-2009.xlsx
@@ -7823,7 +7823,7 @@
         </is>
       </c>
       <c r="AT43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
         </is>
       </c>
       <c r="AT44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
@@ -22319,7 +22319,7 @@
         </is>
       </c>
       <c r="AT122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
@@ -22553,7 +22553,7 @@
         </is>
       </c>
       <c r="AT123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU123" t="inlineStr">
         <is>
@@ -37994,7 +37994,7 @@
         </is>
       </c>
       <c r="AT207" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU207" t="inlineStr">
         <is>
@@ -38228,7 +38228,7 @@
         </is>
       </c>
       <c r="AT208" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU208" t="inlineStr">
         <is>
@@ -53669,7 +53669,7 @@
         </is>
       </c>
       <c r="AT292" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU292" t="inlineStr">
         <is>
@@ -53903,7 +53903,7 @@
         </is>
       </c>
       <c r="AT293" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU293" t="inlineStr">
         <is>

--- a/diseases/d059/2005-2009.xlsx
+++ b/diseases/d059/2005-2009.xlsx
@@ -1164,6 +1164,11 @@
       <c r="R4" t="n">
         <v>0</v>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1176,12 +1181,22 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1538,6 +1553,11 @@
       <c r="R6" t="n">
         <v>0</v>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1550,12 +1570,22 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -2069,6 +2099,11 @@
       <c r="R9" t="n">
         <v>0</v>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2081,12 +2116,22 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -2204,6 +2249,11 @@
       <c r="R10" t="n">
         <v>0</v>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2216,12 +2266,22 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2342,6 +2402,11 @@
       <c r="R11" t="n">
         <v>0</v>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2354,12 +2419,22 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2477,6 +2552,11 @@
       <c r="R12" t="n">
         <v>0</v>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2489,12 +2569,22 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2615,6 +2705,11 @@
       <c r="R13" t="n">
         <v>0</v>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2627,12 +2722,22 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2750,6 +2855,11 @@
       <c r="R14" t="n">
         <v>0</v>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2762,12 +2872,22 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2888,6 +3008,11 @@
       <c r="R15" t="n">
         <v>0</v>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2900,12 +3025,22 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -3023,6 +3158,11 @@
       <c r="R16" t="n">
         <v>0</v>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3035,12 +3175,22 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3161,6 +3311,11 @@
       <c r="R17" t="n">
         <v>0</v>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3173,12 +3328,22 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3296,6 +3461,11 @@
       <c r="R18" t="n">
         <v>0</v>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3308,12 +3478,22 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3434,6 +3614,11 @@
       <c r="R19" t="n">
         <v>0</v>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3446,12 +3631,22 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3569,6 +3764,11 @@
       <c r="R20" t="n">
         <v>0</v>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3581,12 +3781,22 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3707,6 +3917,11 @@
       <c r="R21" t="n">
         <v>0</v>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3719,12 +3934,22 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3842,6 +4067,11 @@
       <c r="R22" t="n">
         <v>0</v>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3854,12 +4084,22 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -3980,6 +4220,11 @@
       <c r="R23" t="n">
         <v>0</v>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3992,12 +4237,22 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -4115,6 +4370,11 @@
       <c r="R24" t="n">
         <v>0</v>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4127,12 +4387,22 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4253,6 +4523,11 @@
       <c r="R25" t="n">
         <v>0</v>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4265,12 +4540,22 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4388,6 +4673,11 @@
       <c r="R26" t="n">
         <v>0</v>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4400,12 +4690,22 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4526,6 +4826,11 @@
       <c r="R27" t="n">
         <v>0</v>
       </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4538,12 +4843,22 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4661,6 +4976,11 @@
       <c r="R28" t="n">
         <v>0</v>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4673,12 +4993,22 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4799,6 +5129,11 @@
       <c r="R29" t="n">
         <v>0</v>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4811,12 +5146,22 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -4934,6 +5279,11 @@
       <c r="R30" t="n">
         <v>0</v>
       </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4946,12 +5296,22 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -9788,6 +10148,11 @@
       <c r="R55" t="n">
         <v>0</v>
       </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9800,12 +10165,22 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
@@ -11351,6 +11726,11 @@
       <c r="R63" t="n">
         <v>0</v>
       </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11363,12 +11743,22 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -15812,6 +16202,11 @@
       <c r="R86" t="n">
         <v>0</v>
       </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15824,12 +16219,22 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR86" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="n">
         <v>0</v>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
@@ -15947,6 +16352,11 @@
       <c r="R87" t="n">
         <v>0</v>
       </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15959,12 +16369,22 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="n">
         <v>0</v>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
@@ -16085,6 +16505,11 @@
       <c r="R88" t="n">
         <v>0</v>
       </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16097,12 +16522,22 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="n">
         <v>0</v>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
@@ -16220,6 +16655,11 @@
       <c r="R89" t="n">
         <v>0</v>
       </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16232,12 +16672,22 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="n">
         <v>0</v>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
@@ -16358,6 +16808,11 @@
       <c r="R90" t="n">
         <v>0</v>
       </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16370,12 +16825,22 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="n">
         <v>0</v>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
@@ -16493,6 +16958,11 @@
       <c r="R91" t="n">
         <v>0</v>
       </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16505,12 +16975,22 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR91" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="n">
         <v>0</v>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
@@ -16631,6 +17111,11 @@
       <c r="R92" t="n">
         <v>0</v>
       </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16643,12 +17128,22 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR92" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="n">
         <v>0</v>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
@@ -16766,6 +17261,11 @@
       <c r="R93" t="n">
         <v>0</v>
       </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16778,12 +17278,22 @@
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR93" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="n">
         <v>0</v>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
@@ -16904,6 +17414,11 @@
       <c r="R94" t="n">
         <v>0</v>
       </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16916,12 +17431,22 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR94" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="n">
         <v>0</v>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
@@ -17039,6 +17564,11 @@
       <c r="R95" t="n">
         <v>0</v>
       </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17051,12 +17581,22 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="n">
         <v>0</v>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
@@ -17177,6 +17717,11 @@
       <c r="R96" t="n">
         <v>0</v>
       </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17189,12 +17734,22 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="n">
         <v>0</v>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
@@ -17312,6 +17867,11 @@
       <c r="R97" t="n">
         <v>0</v>
       </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17324,12 +17884,22 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="n">
         <v>0</v>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
@@ -17450,6 +18020,11 @@
       <c r="R98" t="n">
         <v>0</v>
       </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17462,12 +18037,22 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR98" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="n">
         <v>0</v>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
@@ -17585,6 +18170,11 @@
       <c r="R99" t="n">
         <v>0</v>
       </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17597,12 +18187,22 @@
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR99" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="n">
         <v>0</v>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
@@ -17723,6 +18323,11 @@
       <c r="R100" t="n">
         <v>0</v>
       </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17735,12 +18340,22 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR100" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="n">
         <v>0</v>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
@@ -17858,6 +18473,11 @@
       <c r="R101" t="n">
         <v>0</v>
       </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17870,12 +18490,22 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="n">
         <v>0</v>
+      </c>
+      <c r="AU101" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
@@ -17996,6 +18626,11 @@
       <c r="R102" t="n">
         <v>0</v>
       </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18008,12 +18643,22 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR102" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr"/>
       <c r="AT102" t="n">
         <v>0</v>
+      </c>
+      <c r="AU102" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
@@ -18131,6 +18776,11 @@
       <c r="R103" t="n">
         <v>0</v>
       </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18143,12 +18793,22 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR103" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr"/>
       <c r="AT103" t="n">
         <v>0</v>
+      </c>
+      <c r="AU103" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
@@ -18269,6 +18929,11 @@
       <c r="R104" t="n">
         <v>0</v>
       </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18281,12 +18946,22 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr"/>
       <c r="AT104" t="n">
         <v>0</v>
+      </c>
+      <c r="AU104" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
@@ -18404,6 +19079,11 @@
       <c r="R105" t="n">
         <v>0</v>
       </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18416,12 +19096,22 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr"/>
       <c r="AT105" t="n">
         <v>0</v>
+      </c>
+      <c r="AU105" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
@@ -18542,6 +19232,11 @@
       <c r="R106" t="n">
         <v>0</v>
       </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18554,12 +19249,22 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr"/>
       <c r="AT106" t="n">
         <v>0</v>
+      </c>
+      <c r="AU106" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
@@ -18677,6 +19382,11 @@
       <c r="R107" t="n">
         <v>0</v>
       </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18689,12 +19399,22 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr"/>
       <c r="AT107" t="n">
         <v>0</v>
+      </c>
+      <c r="AU107" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
@@ -24317,6 +25037,11 @@
       <c r="R136" t="n">
         <v>0</v>
       </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24329,12 +25054,22 @@
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR136" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr"/>
       <c r="AT136" t="n">
         <v>0</v>
+      </c>
+      <c r="AU136" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
@@ -25880,6 +26615,11 @@
       <c r="R144" t="n">
         <v>0</v>
       </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25892,12 +26632,22 @@
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR144" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS144" t="inlineStr"/>
       <c r="AT144" t="n">
         <v>0</v>
+      </c>
+      <c r="AU144" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV144" t="inlineStr">
         <is>
@@ -30734,6 +31484,11 @@
       <c r="R169" t="n">
         <v>0</v>
       </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -30746,12 +31501,22 @@
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR169" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS169" t="inlineStr"/>
       <c r="AT169" t="n">
         <v>0</v>
+      </c>
+      <c r="AU169" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
@@ -30869,6 +31634,11 @@
       <c r="R170" t="n">
         <v>0</v>
       </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -30881,12 +31651,22 @@
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR170" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS170" t="inlineStr"/>
       <c r="AT170" t="n">
         <v>0</v>
+      </c>
+      <c r="AU170" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV170" t="inlineStr">
         <is>
@@ -31007,6 +31787,11 @@
       <c r="R171" t="n">
         <v>0</v>
       </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -31019,12 +31804,22 @@
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR171" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS171" t="inlineStr"/>
       <c r="AT171" t="n">
         <v>0</v>
+      </c>
+      <c r="AU171" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV171" t="inlineStr">
         <is>
@@ -31142,6 +31937,11 @@
       <c r="R172" t="n">
         <v>0</v>
       </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -31154,12 +31954,22 @@
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR172" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS172" t="inlineStr"/>
       <c r="AT172" t="n">
         <v>0</v>
+      </c>
+      <c r="AU172" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV172" t="inlineStr">
         <is>
@@ -31280,6 +32090,11 @@
       <c r="R173" t="n">
         <v>0</v>
       </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA173" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -31292,12 +32107,22 @@
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR173" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS173" t="inlineStr"/>
       <c r="AT173" t="n">
         <v>0</v>
+      </c>
+      <c r="AU173" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
@@ -31415,6 +32240,11 @@
       <c r="R174" t="n">
         <v>0</v>
       </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA174" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -31427,12 +32257,22 @@
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR174" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS174" t="inlineStr"/>
       <c r="AT174" t="n">
         <v>0</v>
+      </c>
+      <c r="AU174" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
@@ -31553,6 +32393,11 @@
       <c r="R175" t="n">
         <v>0</v>
       </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA175" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -31565,12 +32410,22 @@
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR175" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS175" t="inlineStr"/>
       <c r="AT175" t="n">
         <v>0</v>
+      </c>
+      <c r="AU175" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV175" t="inlineStr">
         <is>
@@ -31688,6 +32543,11 @@
       <c r="R176" t="n">
         <v>0</v>
       </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA176" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -31700,12 +32560,22 @@
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR176" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS176" t="inlineStr"/>
       <c r="AT176" t="n">
         <v>0</v>
+      </c>
+      <c r="AU176" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV176" t="inlineStr">
         <is>
@@ -31826,6 +32696,11 @@
       <c r="R177" t="n">
         <v>0</v>
       </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA177" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -31838,12 +32713,22 @@
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR177" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS177" t="inlineStr"/>
       <c r="AT177" t="n">
         <v>0</v>
+      </c>
+      <c r="AU177" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV177" t="inlineStr">
         <is>
@@ -31961,6 +32846,11 @@
       <c r="R178" t="n">
         <v>0</v>
       </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA178" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -31973,12 +32863,22 @@
       </c>
       <c r="AP178" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR178" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS178" t="inlineStr"/>
       <c r="AT178" t="n">
         <v>0</v>
+      </c>
+      <c r="AU178" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV178" t="inlineStr">
         <is>
@@ -32099,6 +32999,11 @@
       <c r="R179" t="n">
         <v>0</v>
       </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA179" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32111,12 +33016,22 @@
       </c>
       <c r="AP179" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR179" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS179" t="inlineStr"/>
       <c r="AT179" t="n">
         <v>0</v>
+      </c>
+      <c r="AU179" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV179" t="inlineStr">
         <is>
@@ -32234,6 +33149,11 @@
       <c r="R180" t="n">
         <v>0</v>
       </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA180" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32246,12 +33166,22 @@
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR180" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS180" t="inlineStr"/>
       <c r="AT180" t="n">
         <v>0</v>
+      </c>
+      <c r="AU180" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV180" t="inlineStr">
         <is>
@@ -32372,6 +33302,11 @@
       <c r="R181" t="n">
         <v>0</v>
       </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA181" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32384,12 +33319,22 @@
       </c>
       <c r="AP181" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR181" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS181" t="inlineStr"/>
       <c r="AT181" t="n">
         <v>0</v>
+      </c>
+      <c r="AU181" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV181" t="inlineStr">
         <is>
@@ -32507,6 +33452,11 @@
       <c r="R182" t="n">
         <v>0</v>
       </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA182" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32519,12 +33469,22 @@
       </c>
       <c r="AP182" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR182" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS182" t="inlineStr"/>
       <c r="AT182" t="n">
         <v>0</v>
+      </c>
+      <c r="AU182" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV182" t="inlineStr">
         <is>
@@ -32645,6 +33605,11 @@
       <c r="R183" t="n">
         <v>0</v>
       </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA183" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32657,12 +33622,22 @@
       </c>
       <c r="AP183" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR183" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS183" t="inlineStr"/>
       <c r="AT183" t="n">
         <v>0</v>
+      </c>
+      <c r="AU183" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV183" t="inlineStr">
         <is>
@@ -32780,6 +33755,11 @@
       <c r="R184" t="n">
         <v>0</v>
       </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA184" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32792,12 +33772,22 @@
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR184" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS184" t="inlineStr"/>
       <c r="AT184" t="n">
         <v>0</v>
+      </c>
+      <c r="AU184" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV184" t="inlineStr">
         <is>
@@ -32918,6 +33908,11 @@
       <c r="R185" t="n">
         <v>0</v>
       </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA185" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32930,12 +33925,22 @@
       </c>
       <c r="AP185" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR185" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS185" t="inlineStr"/>
       <c r="AT185" t="n">
         <v>0</v>
+      </c>
+      <c r="AU185" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV185" t="inlineStr">
         <is>
@@ -33053,6 +34058,11 @@
       <c r="R186" t="n">
         <v>0</v>
       </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA186" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33065,12 +34075,22 @@
       </c>
       <c r="AP186" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR186" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS186" t="inlineStr"/>
       <c r="AT186" t="n">
         <v>0</v>
+      </c>
+      <c r="AU186" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV186" t="inlineStr">
         <is>
@@ -33191,6 +34211,11 @@
       <c r="R187" t="n">
         <v>0</v>
       </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA187" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33203,12 +34228,22 @@
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR187" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS187" t="inlineStr"/>
       <c r="AT187" t="n">
         <v>0</v>
+      </c>
+      <c r="AU187" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV187" t="inlineStr">
         <is>
@@ -33326,6 +34361,11 @@
       <c r="R188" t="n">
         <v>0</v>
       </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA188" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33338,12 +34378,22 @@
       </c>
       <c r="AP188" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR188" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS188" t="inlineStr"/>
       <c r="AT188" t="n">
         <v>0</v>
+      </c>
+      <c r="AU188" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV188" t="inlineStr">
         <is>
@@ -33464,6 +34514,11 @@
       <c r="R189" t="n">
         <v>0</v>
       </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA189" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33476,12 +34531,22 @@
       </c>
       <c r="AP189" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR189" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS189" t="inlineStr"/>
       <c r="AT189" t="n">
         <v>0</v>
+      </c>
+      <c r="AU189" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV189" t="inlineStr">
         <is>
@@ -33599,6 +34664,11 @@
       <c r="R190" t="n">
         <v>0</v>
       </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA190" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33611,12 +34681,22 @@
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR190" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS190" t="inlineStr"/>
       <c r="AT190" t="n">
         <v>0</v>
+      </c>
+      <c r="AU190" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV190" t="inlineStr">
         <is>
@@ -39239,6 +40319,11 @@
       <c r="R219" t="n">
         <v>0</v>
       </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA219" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -39251,12 +40336,22 @@
       </c>
       <c r="AP219" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR219" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS219" t="inlineStr"/>
       <c r="AT219" t="n">
         <v>0</v>
+      </c>
+      <c r="AU219" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV219" t="inlineStr">
         <is>
@@ -40802,6 +41897,11 @@
       <c r="R227" t="n">
         <v>0</v>
       </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA227" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -40814,12 +41914,22 @@
       </c>
       <c r="AP227" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR227" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS227" t="inlineStr"/>
       <c r="AT227" t="n">
         <v>0</v>
+      </c>
+      <c r="AU227" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV227" t="inlineStr">
         <is>
@@ -45656,6 +46766,11 @@
       <c r="R252" t="n">
         <v>0</v>
       </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA252" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -45668,12 +46783,22 @@
       </c>
       <c r="AP252" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR252" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS252" t="inlineStr"/>
       <c r="AT252" t="n">
         <v>0</v>
+      </c>
+      <c r="AU252" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV252" t="inlineStr">
         <is>
@@ -45791,6 +46916,11 @@
       <c r="R253" t="n">
         <v>0</v>
       </c>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA253" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -45803,12 +46933,22 @@
       </c>
       <c r="AP253" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR253" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS253" t="inlineStr"/>
       <c r="AT253" t="n">
         <v>0</v>
+      </c>
+      <c r="AU253" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV253" t="inlineStr">
         <is>
@@ -45929,6 +47069,11 @@
       <c r="R254" t="n">
         <v>0</v>
       </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA254" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -45941,12 +47086,22 @@
       </c>
       <c r="AP254" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR254" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS254" t="inlineStr"/>
       <c r="AT254" t="n">
         <v>0</v>
+      </c>
+      <c r="AU254" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV254" t="inlineStr">
         <is>
@@ -46064,6 +47219,11 @@
       <c r="R255" t="n">
         <v>0</v>
       </c>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA255" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -46076,12 +47236,22 @@
       </c>
       <c r="AP255" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR255" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS255" t="inlineStr"/>
       <c r="AT255" t="n">
         <v>0</v>
+      </c>
+      <c r="AU255" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV255" t="inlineStr">
         <is>
@@ -46202,6 +47372,11 @@
       <c r="R256" t="n">
         <v>0</v>
       </c>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA256" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -46214,12 +47389,22 @@
       </c>
       <c r="AP256" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR256" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS256" t="inlineStr"/>
       <c r="AT256" t="n">
         <v>0</v>
+      </c>
+      <c r="AU256" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV256" t="inlineStr">
         <is>
@@ -46337,6 +47522,11 @@
       <c r="R257" t="n">
         <v>0</v>
       </c>
+      <c r="S257" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA257" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -46349,12 +47539,22 @@
       </c>
       <c r="AP257" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR257" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS257" t="inlineStr"/>
       <c r="AT257" t="n">
         <v>0</v>
+      </c>
+      <c r="AU257" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV257" t="inlineStr">
         <is>
@@ -46475,6 +47675,11 @@
       <c r="R258" t="n">
         <v>0</v>
       </c>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA258" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -46487,12 +47692,22 @@
       </c>
       <c r="AP258" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR258" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS258" t="inlineStr"/>
       <c r="AT258" t="n">
         <v>0</v>
+      </c>
+      <c r="AU258" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV258" t="inlineStr">
         <is>
@@ -46610,6 +47825,11 @@
       <c r="R259" t="n">
         <v>0</v>
       </c>
+      <c r="S259" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA259" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -46622,12 +47842,22 @@
       </c>
       <c r="AP259" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR259" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS259" t="inlineStr"/>
       <c r="AT259" t="n">
         <v>0</v>
+      </c>
+      <c r="AU259" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV259" t="inlineStr">
         <is>
@@ -46748,6 +47978,11 @@
       <c r="R260" t="n">
         <v>0</v>
       </c>
+      <c r="S260" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA260" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -46760,12 +47995,22 @@
       </c>
       <c r="AP260" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR260" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS260" t="inlineStr"/>
       <c r="AT260" t="n">
         <v>0</v>
+      </c>
+      <c r="AU260" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV260" t="inlineStr">
         <is>
@@ -46883,6 +48128,11 @@
       <c r="R261" t="n">
         <v>0</v>
       </c>
+      <c r="S261" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA261" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -46895,12 +48145,22 @@
       </c>
       <c r="AP261" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR261" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS261" t="inlineStr"/>
       <c r="AT261" t="n">
         <v>0</v>
+      </c>
+      <c r="AU261" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV261" t="inlineStr">
         <is>
@@ -47021,6 +48281,11 @@
       <c r="R262" t="n">
         <v>0</v>
       </c>
+      <c r="S262" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA262" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -47033,12 +48298,22 @@
       </c>
       <c r="AP262" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR262" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS262" t="inlineStr"/>
       <c r="AT262" t="n">
         <v>0</v>
+      </c>
+      <c r="AU262" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV262" t="inlineStr">
         <is>
@@ -47156,6 +48431,11 @@
       <c r="R263" t="n">
         <v>0</v>
       </c>
+      <c r="S263" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA263" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -47168,12 +48448,22 @@
       </c>
       <c r="AP263" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR263" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS263" t="inlineStr"/>
       <c r="AT263" t="n">
         <v>0</v>
+      </c>
+      <c r="AU263" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV263" t="inlineStr">
         <is>
@@ -47294,6 +48584,11 @@
       <c r="R264" t="n">
         <v>0</v>
       </c>
+      <c r="S264" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA264" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -47306,12 +48601,22 @@
       </c>
       <c r="AP264" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR264" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS264" t="inlineStr"/>
       <c r="AT264" t="n">
         <v>0</v>
+      </c>
+      <c r="AU264" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV264" t="inlineStr">
         <is>
@@ -47429,6 +48734,11 @@
       <c r="R265" t="n">
         <v>0</v>
       </c>
+      <c r="S265" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA265" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -47441,12 +48751,22 @@
       </c>
       <c r="AP265" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR265" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS265" t="inlineStr"/>
       <c r="AT265" t="n">
         <v>0</v>
+      </c>
+      <c r="AU265" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV265" t="inlineStr">
         <is>
@@ -47567,6 +48887,11 @@
       <c r="R266" t="n">
         <v>0</v>
       </c>
+      <c r="S266" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA266" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -47579,12 +48904,22 @@
       </c>
       <c r="AP266" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR266" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS266" t="inlineStr"/>
       <c r="AT266" t="n">
         <v>0</v>
+      </c>
+      <c r="AU266" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV266" t="inlineStr">
         <is>
@@ -47702,6 +49037,11 @@
       <c r="R267" t="n">
         <v>0</v>
       </c>
+      <c r="S267" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA267" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -47714,12 +49054,22 @@
       </c>
       <c r="AP267" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR267" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS267" t="inlineStr"/>
       <c r="AT267" t="n">
         <v>0</v>
+      </c>
+      <c r="AU267" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV267" t="inlineStr">
         <is>
@@ -47840,6 +49190,11 @@
       <c r="R268" t="n">
         <v>0</v>
       </c>
+      <c r="S268" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA268" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -47852,12 +49207,22 @@
       </c>
       <c r="AP268" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR268" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS268" t="inlineStr"/>
       <c r="AT268" t="n">
         <v>0</v>
+      </c>
+      <c r="AU268" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV268" t="inlineStr">
         <is>
@@ -47975,6 +49340,11 @@
       <c r="R269" t="n">
         <v>0</v>
       </c>
+      <c r="S269" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA269" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -47987,12 +49357,22 @@
       </c>
       <c r="AP269" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR269" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS269" t="inlineStr"/>
       <c r="AT269" t="n">
         <v>0</v>
+      </c>
+      <c r="AU269" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV269" t="inlineStr">
         <is>
@@ -48113,6 +49493,11 @@
       <c r="R270" t="n">
         <v>0</v>
       </c>
+      <c r="S270" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA270" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -48125,12 +49510,22 @@
       </c>
       <c r="AP270" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR270" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS270" t="inlineStr"/>
       <c r="AT270" t="n">
         <v>0</v>
+      </c>
+      <c r="AU270" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV270" t="inlineStr">
         <is>
@@ -48248,6 +49643,11 @@
       <c r="R271" t="n">
         <v>0</v>
       </c>
+      <c r="S271" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA271" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -48260,12 +49660,22 @@
       </c>
       <c r="AP271" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR271" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS271" t="inlineStr"/>
       <c r="AT271" t="n">
         <v>0</v>
+      </c>
+      <c r="AU271" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV271" t="inlineStr">
         <is>
@@ -48386,6 +49796,11 @@
       <c r="R272" t="n">
         <v>0</v>
       </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA272" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -48398,12 +49813,22 @@
       </c>
       <c r="AP272" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR272" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS272" t="inlineStr"/>
       <c r="AT272" t="n">
         <v>0</v>
+      </c>
+      <c r="AU272" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV272" t="inlineStr">
         <is>
@@ -48521,6 +49946,11 @@
       <c r="R273" t="n">
         <v>0</v>
       </c>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA273" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -48533,12 +49963,22 @@
       </c>
       <c r="AP273" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR273" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS273" t="inlineStr"/>
       <c r="AT273" t="n">
         <v>0</v>
+      </c>
+      <c r="AU273" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV273" t="inlineStr">
         <is>
@@ -54161,6 +55601,11 @@
       <c r="R302" t="n">
         <v>0</v>
       </c>
+      <c r="S302" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA302" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -54173,12 +55618,22 @@
       </c>
       <c r="AP302" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR302" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS302" t="inlineStr"/>
       <c r="AT302" t="n">
         <v>0</v>
+      </c>
+      <c r="AU302" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV302" t="inlineStr">
         <is>
@@ -55724,6 +57179,11 @@
       <c r="R310" t="n">
         <v>0</v>
       </c>
+      <c r="S310" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA310" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -55736,12 +57196,22 @@
       </c>
       <c r="AP310" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR310" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS310" t="inlineStr"/>
       <c r="AT310" t="n">
         <v>0</v>
+      </c>
+      <c r="AU310" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV310" t="inlineStr">
         <is>
@@ -60578,6 +62048,11 @@
       <c r="R335" t="n">
         <v>0</v>
       </c>
+      <c r="S335" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA335" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -60590,12 +62065,22 @@
       </c>
       <c r="AP335" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR335" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS335" t="inlineStr"/>
       <c r="AT335" t="n">
         <v>0</v>
+      </c>
+      <c r="AU335" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV335" t="inlineStr">
         <is>
@@ -60713,6 +62198,11 @@
       <c r="R336" t="n">
         <v>0</v>
       </c>
+      <c r="S336" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA336" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -60725,12 +62215,22 @@
       </c>
       <c r="AP336" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR336" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS336" t="inlineStr"/>
       <c r="AT336" t="n">
         <v>0</v>
+      </c>
+      <c r="AU336" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV336" t="inlineStr">
         <is>
@@ -60851,6 +62351,11 @@
       <c r="R337" t="n">
         <v>0</v>
       </c>
+      <c r="S337" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA337" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -60863,12 +62368,22 @@
       </c>
       <c r="AP337" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR337" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS337" t="inlineStr"/>
       <c r="AT337" t="n">
         <v>0</v>
+      </c>
+      <c r="AU337" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV337" t="inlineStr">
         <is>
@@ -60986,6 +62501,11 @@
       <c r="R338" t="n">
         <v>0</v>
       </c>
+      <c r="S338" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA338" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -60998,12 +62518,22 @@
       </c>
       <c r="AP338" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR338" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS338" t="inlineStr"/>
       <c r="AT338" t="n">
         <v>0</v>
+      </c>
+      <c r="AU338" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV338" t="inlineStr">
         <is>
@@ -61124,6 +62654,11 @@
       <c r="R339" t="n">
         <v>0</v>
       </c>
+      <c r="S339" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA339" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -61136,12 +62671,22 @@
       </c>
       <c r="AP339" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR339" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS339" t="inlineStr"/>
       <c r="AT339" t="n">
         <v>0</v>
+      </c>
+      <c r="AU339" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV339" t="inlineStr">
         <is>
@@ -61259,6 +62804,11 @@
       <c r="R340" t="n">
         <v>0</v>
       </c>
+      <c r="S340" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA340" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -61271,12 +62821,22 @@
       </c>
       <c r="AP340" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR340" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS340" t="inlineStr"/>
       <c r="AT340" t="n">
         <v>0</v>
+      </c>
+      <c r="AU340" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV340" t="inlineStr">
         <is>
@@ -61397,6 +62957,11 @@
       <c r="R341" t="n">
         <v>0</v>
       </c>
+      <c r="S341" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA341" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -61409,12 +62974,22 @@
       </c>
       <c r="AP341" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR341" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS341" t="inlineStr"/>
       <c r="AT341" t="n">
         <v>0</v>
+      </c>
+      <c r="AU341" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV341" t="inlineStr">
         <is>
@@ -61532,6 +63107,11 @@
       <c r="R342" t="n">
         <v>0</v>
       </c>
+      <c r="S342" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA342" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -61544,12 +63124,22 @@
       </c>
       <c r="AP342" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR342" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS342" t="inlineStr"/>
       <c r="AT342" t="n">
         <v>0</v>
+      </c>
+      <c r="AU342" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV342" t="inlineStr">
         <is>
@@ -61670,6 +63260,11 @@
       <c r="R343" t="n">
         <v>0</v>
       </c>
+      <c r="S343" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA343" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -61682,12 +63277,22 @@
       </c>
       <c r="AP343" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR343" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS343" t="inlineStr"/>
       <c r="AT343" t="n">
         <v>0</v>
+      </c>
+      <c r="AU343" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV343" t="inlineStr">
         <is>
@@ -61805,6 +63410,11 @@
       <c r="R344" t="n">
         <v>0</v>
       </c>
+      <c r="S344" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA344" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -61817,12 +63427,22 @@
       </c>
       <c r="AP344" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR344" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS344" t="inlineStr"/>
       <c r="AT344" t="n">
         <v>0</v>
+      </c>
+      <c r="AU344" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV344" t="inlineStr">
         <is>
@@ -61943,6 +63563,11 @@
       <c r="R345" t="n">
         <v>0</v>
       </c>
+      <c r="S345" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA345" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -61955,12 +63580,22 @@
       </c>
       <c r="AP345" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR345" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS345" t="inlineStr"/>
       <c r="AT345" t="n">
         <v>0</v>
+      </c>
+      <c r="AU345" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV345" t="inlineStr">
         <is>
@@ -62078,6 +63713,11 @@
       <c r="R346" t="n">
         <v>0</v>
       </c>
+      <c r="S346" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA346" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -62090,12 +63730,22 @@
       </c>
       <c r="AP346" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR346" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS346" t="inlineStr"/>
       <c r="AT346" t="n">
         <v>0</v>
+      </c>
+      <c r="AU346" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV346" t="inlineStr">
         <is>
@@ -62216,6 +63866,11 @@
       <c r="R347" t="n">
         <v>0</v>
       </c>
+      <c r="S347" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA347" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -62228,12 +63883,22 @@
       </c>
       <c r="AP347" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR347" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS347" t="inlineStr"/>
       <c r="AT347" t="n">
         <v>0</v>
+      </c>
+      <c r="AU347" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV347" t="inlineStr">
         <is>
@@ -62351,6 +64016,11 @@
       <c r="R348" t="n">
         <v>0</v>
       </c>
+      <c r="S348" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA348" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -62363,12 +64033,22 @@
       </c>
       <c r="AP348" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR348" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS348" t="inlineStr"/>
       <c r="AT348" t="n">
         <v>0</v>
+      </c>
+      <c r="AU348" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV348" t="inlineStr">
         <is>
@@ -62489,6 +64169,11 @@
       <c r="R349" t="n">
         <v>0</v>
       </c>
+      <c r="S349" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA349" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -62501,12 +64186,22 @@
       </c>
       <c r="AP349" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR349" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS349" t="inlineStr"/>
       <c r="AT349" t="n">
         <v>0</v>
+      </c>
+      <c r="AU349" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV349" t="inlineStr">
         <is>
@@ -62624,6 +64319,11 @@
       <c r="R350" t="n">
         <v>0</v>
       </c>
+      <c r="S350" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA350" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -62636,12 +64336,22 @@
       </c>
       <c r="AP350" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR350" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS350" t="inlineStr"/>
       <c r="AT350" t="n">
         <v>0</v>
+      </c>
+      <c r="AU350" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV350" t="inlineStr">
         <is>
@@ -62762,6 +64472,11 @@
       <c r="R351" t="n">
         <v>0</v>
       </c>
+      <c r="S351" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA351" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -62774,12 +64489,22 @@
       </c>
       <c r="AP351" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR351" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS351" t="inlineStr"/>
       <c r="AT351" t="n">
         <v>0</v>
+      </c>
+      <c r="AU351" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV351" t="inlineStr">
         <is>
@@ -62897,6 +64622,11 @@
       <c r="R352" t="n">
         <v>0</v>
       </c>
+      <c r="S352" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA352" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -62909,12 +64639,22 @@
       </c>
       <c r="AP352" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR352" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS352" t="inlineStr"/>
       <c r="AT352" t="n">
         <v>0</v>
+      </c>
+      <c r="AU352" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV352" t="inlineStr">
         <is>
@@ -63035,6 +64775,11 @@
       <c r="R353" t="n">
         <v>0</v>
       </c>
+      <c r="S353" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA353" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -63047,12 +64792,22 @@
       </c>
       <c r="AP353" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR353" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS353" t="inlineStr"/>
       <c r="AT353" t="n">
         <v>0</v>
+      </c>
+      <c r="AU353" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV353" t="inlineStr">
         <is>
@@ -63170,6 +64925,11 @@
       <c r="R354" t="n">
         <v>0</v>
       </c>
+      <c r="S354" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA354" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -63182,12 +64942,22 @@
       </c>
       <c r="AP354" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR354" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS354" t="inlineStr"/>
       <c r="AT354" t="n">
         <v>0</v>
+      </c>
+      <c r="AU354" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV354" t="inlineStr">
         <is>
@@ -63308,6 +65078,11 @@
       <c r="R355" t="n">
         <v>0</v>
       </c>
+      <c r="S355" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA355" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -63320,12 +65095,22 @@
       </c>
       <c r="AP355" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR355" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS355" t="inlineStr"/>
       <c r="AT355" t="n">
         <v>0</v>
+      </c>
+      <c r="AU355" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV355" t="inlineStr">
         <is>
@@ -63443,6 +65228,11 @@
       <c r="R356" t="n">
         <v>0</v>
       </c>
+      <c r="S356" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA356" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -63455,12 +65245,22 @@
       </c>
       <c r="AP356" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR356" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS356" t="inlineStr"/>
       <c r="AT356" t="n">
         <v>0</v>
+      </c>
+      <c r="AU356" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV356" t="inlineStr">
         <is>
